--- a/InputData/indst/IEMUEF/Indst Eqpt Min Unit E Factor.xlsx
+++ b/InputData/indst/IEMUEF/Indst Eqpt Min Unit E Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IEMUEF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914363E8-B62F-4FE3-9F10-79658097D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADEAAB6-28F7-40BD-9A4D-9855BE142785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="684" firstSheet="3" activeTab="9" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
+    <workbookView xWindow="1290" yWindow="260" windowWidth="17790" windowHeight="9120" tabRatio="684" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,200 @@
     <sheet name="High Temp" sheetId="12" r:id="rId7"/>
     <sheet name="Cooling" sheetId="11" r:id="rId8"/>
     <sheet name="Electrochemical" sheetId="14" r:id="rId9"/>
-    <sheet name="IEMUEF" sheetId="2" r:id="rId10"/>
+    <sheet name="Other" sheetId="15" r:id="rId10"/>
+    <sheet name="References" sheetId="16" r:id="rId11"/>
+    <sheet name="IEMUEF" sheetId="2" r:id="rId12"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="base.year">#REF!</definedName>
+    <definedName name="CH4_to_CO2e">'[2]Cross-Page Data'!$C$12</definedName>
+    <definedName name="CH4GWP">#REF!</definedName>
+    <definedName name="coal.past">#REF!</definedName>
+    <definedName name="Constants.Density.Diesel">#REF!</definedName>
+    <definedName name="Constants.Density.Ethanol">#REF!</definedName>
+    <definedName name="Constants.Density.JetFuel">#REF!</definedName>
+    <definedName name="Constants.Density.MotorSpirit">#REF!</definedName>
+    <definedName name="Conversion.to.average.power">#REF!</definedName>
+    <definedName name="Conversion.water.L">#REF!</definedName>
+    <definedName name="Conversion.water.units">#REF!</definedName>
+    <definedName name="Conversions.Area.m2">#REF!</definedName>
+    <definedName name="Conversions.Area.Units">#REF!</definedName>
+    <definedName name="Conversions.Energy.Joules">#REF!</definedName>
+    <definedName name="Conversions.Energy.Units">#REF!</definedName>
+    <definedName name="Conversions.Money.GBP">#REF!</definedName>
+    <definedName name="Conversions.Money.Units">#REF!</definedName>
+    <definedName name="Conversions.Power.Units">#REF!</definedName>
+    <definedName name="Conversions.Power.Watts">#REF!</definedName>
+    <definedName name="Cost.Capital.Scenario">#REF!</definedName>
+    <definedName name="Cost.Finance.Scenario">#REF!</definedName>
+    <definedName name="Cost.Fuel.Scenario">#REF!</definedName>
+    <definedName name="Cost.Infrastructure.Scenario">#REF!</definedName>
+    <definedName name="cpi_2010to2012">#REF!</definedName>
+    <definedName name="cpi_2013to2012">#REF!</definedName>
+    <definedName name="cpi_2014to2012">#REF!</definedName>
+    <definedName name="cpi_2016to2012">#REF!</definedName>
+    <definedName name="csp.capacity">#REF!</definedName>
+    <definedName name="D">#REF!</definedName>
+    <definedName name="discount_factors">#REF!</definedName>
+    <definedName name="EF.BlastFurnaceGas.CO2">#REF!</definedName>
+    <definedName name="EF.Diesel.CH4">#REF!</definedName>
+    <definedName name="EF.Diesel.CO2">#REF!</definedName>
+    <definedName name="EF.Diesel.N2O">#REF!</definedName>
+    <definedName name="EF.IndustrialCoal.CH4">#REF!</definedName>
+    <definedName name="EF.IndustrialCoal.CO2">#REF!</definedName>
+    <definedName name="EF.IndustrialCoal.N2O">#REF!</definedName>
+    <definedName name="EF.NaturalGas.CH4">#REF!</definedName>
+    <definedName name="EF.NaturalGas.CO2">#REF!</definedName>
+    <definedName name="EF.NaturalGas.N2O">#REF!</definedName>
+    <definedName name="GBP">#REF!</definedName>
+    <definedName name="gigwatts_to_megawatts">[3]About!$A$31</definedName>
+    <definedName name="growth.scenario">#REF!</definedName>
+    <definedName name="GWP.CH4">#REF!</definedName>
+    <definedName name="GWP.N2O">#REF!</definedName>
+    <definedName name="GWPCH4">#REF!</definedName>
+    <definedName name="GWPN2O">#REF!</definedName>
+    <definedName name="h">#REF!</definedName>
+    <definedName name="I.01">#REF!</definedName>
+    <definedName name="I.a.scenario">#REF!</definedName>
+    <definedName name="I.b.scenario">#REF!</definedName>
+    <definedName name="I.b.scenario.efficiency">#REF!</definedName>
+    <definedName name="I.c.scenario">#REF!</definedName>
+    <definedName name="I.c.scenario.fuelmix">#REF!</definedName>
+    <definedName name="II.scenario">#REF!</definedName>
+    <definedName name="III.scenario">#REF!</definedName>
+    <definedName name="input.choice">#REF!</definedName>
+    <definedName name="INR">#REF!</definedName>
+    <definedName name="INRb">#REF!</definedName>
+    <definedName name="INRCr">#REF!</definedName>
+    <definedName name="INRLac">#REF!</definedName>
+    <definedName name="INRt">#REF!</definedName>
+    <definedName name="IV.a.scenario">#REF!</definedName>
+    <definedName name="IV.b.scenario">#REF!</definedName>
+    <definedName name="IV.c.1.scenario">#REF!</definedName>
+    <definedName name="iv.c.2.scenario">#REF!</definedName>
+    <definedName name="IV.d.scenario">#REF!</definedName>
+    <definedName name="IV.e.scenario">#REF!</definedName>
+    <definedName name="IV.f.scenario">#REF!</definedName>
+    <definedName name="IX.a.scenario">#REF!</definedName>
+    <definedName name="MGBP">#REF!</definedName>
+    <definedName name="Minesize.xv.b">#REF!</definedName>
+    <definedName name="N2O_to_CO2e">'[2]Cross-Page Data'!$C$13</definedName>
+    <definedName name="N2OGWP">#REF!</definedName>
+    <definedName name="nuclear.past">#REF!</definedName>
+    <definedName name="plantsize.I.b">#REF!</definedName>
+    <definedName name="Plantsize.II">#REF!</definedName>
+    <definedName name="Plantsize.III">#REF!</definedName>
+    <definedName name="plantsize.iv.a">#REF!</definedName>
+    <definedName name="plantsize.iv.b">#REF!</definedName>
+    <definedName name="Plantsize.iv.c.1">#REF!</definedName>
+    <definedName name="plantsize.iv.c.2">#REF!</definedName>
+    <definedName name="plantsize.iv.d">#REF!</definedName>
+    <definedName name="predefined.scenario">#REF!</definedName>
+    <definedName name="Preferences.AreaUnits">#REF!</definedName>
+    <definedName name="preferences.energyunits">#REF!</definedName>
+    <definedName name="Preferences.moneyunits">#REF!</definedName>
+    <definedName name="Preferences.PowerUnits">#REF!</definedName>
+    <definedName name="Preferences.Unit.Energy">#REF!</definedName>
+    <definedName name="Preferences.Unit.Power">#REF!</definedName>
+    <definedName name="Preferences.waterunit">#REF!</definedName>
+    <definedName name="Print_Area_MI">#REF!</definedName>
+    <definedName name="Reliability.scenario">#REF!</definedName>
+    <definedName name="small_hydro.capacity">#REF!</definedName>
+    <definedName name="target.year">#REF!</definedName>
+    <definedName name="Unit.acre">#REF!</definedName>
+    <definedName name="unit.bcm">#REF!</definedName>
+    <definedName name="Unit.boe">#REF!</definedName>
+    <definedName name="Unit.calorie">#REF!</definedName>
+    <definedName name="Unit.day">#REF!</definedName>
+    <definedName name="Unit.GJ">#REF!</definedName>
+    <definedName name="Unit.GW">#REF!</definedName>
+    <definedName name="Unit.GWh">#REF!</definedName>
+    <definedName name="Unit.ha">#REF!</definedName>
+    <definedName name="Unit.hour">#REF!</definedName>
+    <definedName name="Unit.J">#REF!</definedName>
+    <definedName name="unit.kcng">#REF!</definedName>
+    <definedName name="unit.kgb">#REF!</definedName>
+    <definedName name="unit.kgce">#REF!</definedName>
+    <definedName name="unit.kghe">#REF!</definedName>
+    <definedName name="unit.kglpge">#REF!</definedName>
+    <definedName name="Unit.km2">#REF!</definedName>
+    <definedName name="Unit.kW">#REF!</definedName>
+    <definedName name="Unit.kWh">#REF!</definedName>
+    <definedName name="unit.L">#REF!</definedName>
+    <definedName name="unit.latfe">#REF!</definedName>
+    <definedName name="unit.lcng">#REF!</definedName>
+    <definedName name="unit.lde">#REF!</definedName>
+    <definedName name="unit.lke">#REF!</definedName>
+    <definedName name="unit.lpe">#REF!</definedName>
+    <definedName name="Unit.m2">#REF!</definedName>
+    <definedName name="Unit.m3">#REF!</definedName>
+    <definedName name="unit.MCM">#REF!</definedName>
+    <definedName name="Unit.minute">#REF!</definedName>
+    <definedName name="Unit.MJ">#REF!</definedName>
+    <definedName name="unit.mmbtu">#REF!</definedName>
+    <definedName name="unit.mmscm">#REF!</definedName>
+    <definedName name="unit.mtcce">#REF!</definedName>
+    <definedName name="Unit.Mtce">#REF!</definedName>
+    <definedName name="unit.mtde">#REF!</definedName>
+    <definedName name="unit.mticce">#REF!</definedName>
+    <definedName name="unit.mtice">#REF!</definedName>
+    <definedName name="unit.mtle">#REF!</definedName>
+    <definedName name="Unit.Mtoe">#REF!</definedName>
+    <definedName name="Unit.MW">#REF!</definedName>
+    <definedName name="Unit.MWh">#REF!</definedName>
+    <definedName name="Unit.PJ">#REF!</definedName>
+    <definedName name="unit.scm">#REF!</definedName>
+    <definedName name="unit.scmb">#REF!</definedName>
+    <definedName name="unit.tce">#REF!</definedName>
+    <definedName name="unit.ticce">#REF!</definedName>
+    <definedName name="unit.tice">#REF!</definedName>
+    <definedName name="Unit.TJ">#REF!</definedName>
+    <definedName name="Unit.toe">#REF!</definedName>
+    <definedName name="Unit.TWh">#REF!</definedName>
+    <definedName name="Unit.W">#REF!</definedName>
+    <definedName name="Unit.year">#REF!</definedName>
+    <definedName name="unit_conv">[4]About!$A$123</definedName>
+    <definedName name="USD_Bn">#REF!</definedName>
+    <definedName name="USD_mn">#REF!</definedName>
+    <definedName name="USD2012_">#REF!</definedName>
+    <definedName name="v.a.scenario">#REF!</definedName>
+    <definedName name="V.b.scenario">#REF!</definedName>
+    <definedName name="V.c.scenario">#REF!</definedName>
+    <definedName name="VI.a.scenario">#REF!</definedName>
+    <definedName name="VII.a.scenario">#REF!</definedName>
+    <definedName name="VII.b.scenario">#REF!</definedName>
+    <definedName name="X.a.economy">#REF!</definedName>
+    <definedName name="X.a.epi">#REF!</definedName>
+    <definedName name="X.a.floorspace">#REF!</definedName>
+    <definedName name="X.b.ac">#REF!</definedName>
+    <definedName name="X.b.ecbc">#REF!</definedName>
+    <definedName name="x.b.floorspace">#REF!</definedName>
+    <definedName name="XI.cement.fuel">#REF!</definedName>
+    <definedName name="XI.fuelmix">#REF!</definedName>
+    <definedName name="XI.scenario">#REF!</definedName>
+    <definedName name="XI.steel.fuel">#REF!</definedName>
+    <definedName name="XII.a.scenario">#REF!</definedName>
+    <definedName name="XII.a.scenario.EVs">#REF!</definedName>
+    <definedName name="XII.a.scenario.mode">#REF!</definedName>
+    <definedName name="XII.a.scenario.pub_pri">#REF!</definedName>
+    <definedName name="XII.b.mode">#REF!</definedName>
+    <definedName name="XII.b.scenario">#REF!</definedName>
+    <definedName name="XIII.a.chulhas">#REF!</definedName>
+    <definedName name="XIII.a.scenario.fuelsplit">#REF!</definedName>
+    <definedName name="XIII.b">#REF!</definedName>
+    <definedName name="XIV.scenario">#REF!</definedName>
+    <definedName name="XIV.scenario.fuelsplit">#REF!</definedName>
+    <definedName name="xv.a.scenario">#REF!</definedName>
+    <definedName name="xv.b.scenario">#REF!</definedName>
+    <definedName name="XV.c.scenario">#REF!</definedName>
+    <definedName name="xvi.scenario.fuelsplit">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -67,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="269">
   <si>
     <t>Source:</t>
   </si>
@@ -636,6 +828,290 @@
   </si>
   <si>
     <t>energy intensity (MIN)</t>
+  </si>
+  <si>
+    <t>Ag tractors (mobile equipment)</t>
+  </si>
+  <si>
+    <t>Tractor</t>
+  </si>
+  <si>
+    <t>η</t>
+  </si>
+  <si>
+    <t>nom P [kW]</t>
+  </si>
+  <si>
+    <t>nom w [rpm]</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ref 19 // </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open circles are added via post processing and represent the weighted</t>
+    </r>
+  </si>
+  <si>
+    <t>unkn.</t>
+  </si>
+  <si>
+    <t>average load &amp; engine speeds from ref 20 scaled by nominal engine speeds</t>
+  </si>
+  <si>
+    <t>4WD / MFWD</t>
+  </si>
+  <si>
+    <t>245/127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric </t>
+  </si>
+  <si>
+    <t>PM Electric Motor</t>
+  </si>
+  <si>
+    <t>150 (overload)</t>
+  </si>
+  <si>
+    <t>charging adjusted</t>
+  </si>
+  <si>
+    <t>22,25</t>
+  </si>
+  <si>
+    <t>Custom autonomous</t>
+  </si>
+  <si>
+    <t>Simulated autonomous</t>
+  </si>
+  <si>
+    <t>Reduction in fuel use</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ref 21 // </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open circles are added via post processing and represent the weighted</t>
+    </r>
+  </si>
+  <si>
+    <t>Ref 20</t>
+  </si>
+  <si>
+    <t>(from figure)</t>
+  </si>
+  <si>
+    <t>Tables 2-5</t>
+  </si>
+  <si>
+    <t>weighted values</t>
+  </si>
+  <si>
+    <t>max t at speed</t>
+  </si>
+  <si>
+    <t>load (fig 16)</t>
+  </si>
+  <si>
+    <t>speed on fig 2</t>
+  </si>
+  <si>
+    <t>speed on fig 14</t>
+  </si>
+  <si>
+    <t>torque on fig 2</t>
+  </si>
+  <si>
+    <t>torque on fig 14</t>
+  </si>
+  <si>
+    <t>% of total field time</t>
+  </si>
+  <si>
+    <t>weighted average torque %</t>
+  </si>
+  <si>
+    <t>weighted average engine speed</t>
+  </si>
+  <si>
+    <t>weighted-average torque</t>
+  </si>
+  <si>
+    <t>weighted-average engine speed</t>
+  </si>
+  <si>
+    <t>Field operation</t>
+  </si>
+  <si>
+    <t>t (%)</t>
+  </si>
+  <si>
+    <t>w (s^-1)</t>
+  </si>
+  <si>
+    <t>TS-I</t>
+  </si>
+  <si>
+    <t>TS-II</t>
+  </si>
+  <si>
+    <t>TS-III</t>
+  </si>
+  <si>
+    <t>NH3 application</t>
+  </si>
+  <si>
+    <t>Field cultivation</t>
+  </si>
+  <si>
+    <t>Corn planting</t>
+  </si>
+  <si>
+    <t>Reference Number</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Page or Table</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>D. Friso</t>
+  </si>
+  <si>
+    <t>Brake Thermal Efficiency and BSFC of Diesel  Engines: Mathematical Modeling and Comparison  between Diesel Oil and Biodiesel Fueling</t>
+  </si>
+  <si>
+    <t>https://www.m-hikari.com/ams/ams-2014/ams-129-132-2014/frisoAMS129-132-2014-1.pdf</t>
+  </si>
+  <si>
+    <t>S. Pitla, J.D. Luck, J. Werner, N. Line, S.A. Shearer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-field fuel use and load states of agricultural field machinery </t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0168169916000041</t>
+  </si>
+  <si>
+    <t>D. Troncon, L. Alberti</t>
+  </si>
+  <si>
+    <t>Case of Study of the Electrification of a Tractor: Electric Motor Performance Requirements and Design</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/1996-1073/13/9/2197</t>
+  </si>
+  <si>
+    <t>Z. Shao, S. Anup</t>
+  </si>
+  <si>
+    <t>Incentives for electrifying agricultural tractors in India</t>
+  </si>
+  <si>
+    <t>https://theicct.org/publication/india-hvs-evs-incentives-elec-tractors-india-oct22/</t>
+  </si>
+  <si>
+    <t>O. Lagnelov et al.</t>
+  </si>
+  <si>
+    <t>Cost analysis of autonomous battery electric field tractors in agriculture</t>
+  </si>
+  <si>
+    <t>https://pub.epsilon.slu.se/id/document/20368600</t>
+  </si>
+  <si>
+    <t>J. Engstrom and O. Lagnelov</t>
+  </si>
+  <si>
+    <t>An Autonomous Electric Powered Tractor—Simulation of All Operations on a Swedish Dairy Farm</t>
+  </si>
+  <si>
+    <t>https://www.davidpublisher.com/Public/uploads/Contribute/5ba1b8c2036b0.pdf</t>
+  </si>
+  <si>
+    <t>Where the Energy Goes: Electric Cars</t>
+  </si>
+  <si>
+    <t>https://www.fueleconomy.gov/feg/atv-ev.shtml</t>
+  </si>
+  <si>
+    <t>Agricultural tractor efficiency development as a sustainable model and evaluating the implementation of its automation operations: a case study</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/pdf/10.1080/14735903.2025.2546703</t>
+  </si>
+  <si>
+    <t>I. Herranz-Matey, L. Ruiz-Garcia</t>
+  </si>
+  <si>
+    <t>Present day efficiencies</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t># generations</t>
+  </si>
+  <si>
+    <t>yr/generation</t>
+  </si>
+  <si>
+    <t>linear coef.</t>
+  </si>
+  <si>
+    <t>change/yr</t>
+  </si>
+  <si>
+    <t>Historical Change in Tractor Energy Intensity</t>
+  </si>
+  <si>
+    <t>Assume minimum E factor is if historical efficiency gains continue through the model run</t>
+  </si>
+  <si>
+    <t>For electricity, scale this efficiency improvement by the ratio of electricity to combustion improvements</t>
+  </si>
+  <si>
+    <t>in the AEO baseline.</t>
+  </si>
+  <si>
+    <t>Electric</t>
   </si>
 </sst>
 </file>
@@ -704,7 +1180,7 @@
       <name val="Segoeui"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -735,6 +1211,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -750,7 +1232,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -783,6 +1265,29 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1316,6 +1821,335 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>216087</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>164825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEBF025F-AE1B-4024-9936-D048F20085FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6407150" y="736600"/>
+          <a:ext cx="4483287" cy="2190476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>122869</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>160057</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{950A5A3B-1668-4B2E-B77C-F5D3553DFC9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6407150" y="3683000"/>
+          <a:ext cx="2561269" cy="2185707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="EIA MECS Table 5.2"/>
+      <sheetName val="Med-High Temp Heat"/>
+      <sheetName val="Low Temp Heat"/>
+      <sheetName val="Cooling"/>
+      <sheetName val="Other"/>
+      <sheetName val="Efficiencies"/>
+      <sheetName val="Temperature Breakdown"/>
+      <sheetName val="References"/>
+      <sheetName val="Mapping"/>
+      <sheetName val="PIFURfE"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Cross-Page Data"/>
+      <sheetName val="Non-Energy FF CO2 Emissions"/>
+      <sheetName val="Cement CO2 Emissions"/>
+      <sheetName val="Iron and Steel"/>
+      <sheetName val="Coal Mining"/>
+      <sheetName val="Natural Gas Systems"/>
+      <sheetName val="Petroleum Systems"/>
+      <sheetName val="Chem - HCFC 22 Production"/>
+      <sheetName val="Chem - ODS"/>
+      <sheetName val="Other - Aluminum"/>
+      <sheetName val="Other - Magnesium"/>
+      <sheetName val="Other - Semiconductor Mfg"/>
+      <sheetName val="Other - Elec Trans and Dist"/>
+      <sheetName val="Agriculture - EF &amp; Manure Mgmt"/>
+      <sheetName val="Agriculture - Rice Cultivation"/>
+      <sheetName val="Agriculture - Soil Mgmt"/>
+      <sheetName val="Waste - Landfills"/>
+      <sheetName val="Waste - Water Treatment"/>
+      <sheetName val="Other Industrial Processes"/>
+      <sheetName val="Combined Data"/>
+      <sheetName val="BPEiC-CO2"/>
+      <sheetName val="BPEiC-CH4"/>
+      <sheetName val="BPEiC-N2O"/>
+      <sheetName val="BPEiC-F-gases"/>
+      <sheetName val="EPA (2017) Table A3.6-1"/>
+      <sheetName val="EPA (2017) Table A3.6-7"/>
+      <sheetName val="EPA (2017) Table A3.6-10"/>
+      <sheetName val="AEO 2017_Table 6"/>
+      <sheetName val="AEO 2017_Table 11"/>
+      <sheetName val="AEO 2017_Table 13"/>
+      <sheetName val="AEO 2017_Table 15"/>
+      <sheetName val="AEO 2017_Table 19"/>
+      <sheetName val="AEO 2017_Table 20"/>
+      <sheetName val="AEO 2017_Table 24"/>
+      <sheetName val="AEO 2017_Table 62"/>
+      <sheetName val="AEO 2016_Table 6"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="C12">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>265</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Transport Refrigeration</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="2035 Report Deployment"/>
+      <sheetName val="2035 Report Data"/>
+      <sheetName val="EPS Output"/>
+      <sheetName val="AEO Table 9"/>
+      <sheetName val="AEO Table 9 (2019)"/>
+      <sheetName val="AEO Table 16"/>
+      <sheetName val="BGBSC"/>
+      <sheetName val="PAGBSC"/>
+      <sheetName val="SYGBSC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="31">
+          <cell r="A31">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Country Selector"/>
+      <sheetName val="Multipliers and Adjustments"/>
+      <sheetName val="EPA Data"/>
+      <sheetName val="Tech to Policy Mapping"/>
+      <sheetName val="SNAP Adjustment"/>
+      <sheetName val="Cement Data"/>
+      <sheetName val="Data Check"/>
+      <sheetName val="PERAC-cement"/>
+      <sheetName val="PERAC-ngps-mthncptr"/>
+      <sheetName val="PERAC-ngps-mthndstr"/>
+      <sheetName val="PERAC-fgassubstitution"/>
+      <sheetName val="PERAC-fgasdestruction"/>
+      <sheetName val="PERAC-fgasrecovery"/>
+      <sheetName val="PERAC-inspctmaintretrofit"/>
+      <sheetName val="PERAC-coalmining-mthncptr"/>
+      <sheetName val="PERAC-coalmining-mthndstr"/>
+      <sheetName val="PERAC-waste-mthncptr"/>
+      <sheetName val="PERAC-waste-mthndstr"/>
+      <sheetName val="PERAC-cropsrice"/>
+      <sheetName val="PERAC-livestock"/>
+      <sheetName val="PERAC-MCD"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="123">
+          <cell r="A123">
+            <v>1000000000000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1867,6 +2701,992 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21FF5BE-8B42-4F7D-84E0-F7A55E52FE3E}">
+  <dimension ref="A1:T45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="27">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="C5" s="12">
+        <f>1/B5</f>
+        <v>3.3003300330033003</v>
+      </c>
+      <c r="D5">
+        <v>58.8</v>
+      </c>
+      <c r="E5">
+        <v>2500</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="27">
+        <f>AVERAGE(0.35,0.305,0.266)</f>
+        <v>0.307</v>
+      </c>
+      <c r="C6" s="12">
+        <f>1/B6</f>
+        <v>3.2573289902280131</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6">
+        <v>2100</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10">
+        <f>AVERAGE(0.836,0.885,0.905)</f>
+        <v>0.87533333333333341</v>
+      </c>
+      <c r="C10">
+        <f>1/B10</f>
+        <v>1.1424219345011424</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10">
+        <v>2600</v>
+      </c>
+      <c r="F10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11">
+        <f>B10*(1-AVERAGE(0.1,0.15))</f>
+        <v>0.76591666666666669</v>
+      </c>
+      <c r="C11">
+        <f>1/B11</f>
+        <v>1.3056250680013055</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="F11" s="28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12">
+        <f>1/C12</f>
+        <v>0.64890826648064182</v>
+      </c>
+      <c r="C12">
+        <f>AVERAGE(C5:C6)*(1-AVERAGE(0.52,0.54))</f>
+        <v>1.5410498704593585</v>
+      </c>
+      <c r="D12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13">
+        <f>1/C13</f>
+        <v>0.72615925058548003</v>
+      </c>
+      <c r="C13">
+        <f>AVERAGE(C5:C6)*(1-AVERAGE(0.58))</f>
+        <v>1.3771083948785758</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="F13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="14">
+        <f>(AVERAGE(C5:C6)-AVERAGE(C11:C13))/AVERAGE(C5:C6)</f>
+        <v>0.57060049240377109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="25"/>
+      <c r="B17" s="14"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C20" t="s">
+        <v>260</v>
+      </c>
+      <c r="D20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" t="s">
+        <v>263</v>
+      </c>
+      <c r="H20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B21" s="32">
+        <f>-0.041</f>
+        <v>-4.1000000000000002E-2</v>
+      </c>
+      <c r="C21" s="18">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <f>(2021-1989)/C21</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="E21" s="13">
+        <f>B21/D21</f>
+        <v>-8.968750000000001E-3</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="E23" s="17">
+        <f>E21*'BAU Efficiency Improvements'!M25/'BAU Efficiency Improvements'!M24</f>
+        <v>-4.7694685902703029E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" t="s">
+        <v>210</v>
+      </c>
+      <c r="G36" t="s">
+        <v>211</v>
+      </c>
+      <c r="H36" t="s">
+        <v>212</v>
+      </c>
+      <c r="I36" t="s">
+        <v>213</v>
+      </c>
+      <c r="J36" t="s">
+        <v>214</v>
+      </c>
+      <c r="M36" t="s">
+        <v>215</v>
+      </c>
+      <c r="P36" t="s">
+        <v>216</v>
+      </c>
+      <c r="S36" t="s">
+        <v>217</v>
+      </c>
+      <c r="T36" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" t="s">
+        <v>219</v>
+      </c>
+      <c r="B37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" t="s">
+        <v>221</v>
+      </c>
+      <c r="J37" t="s">
+        <v>222</v>
+      </c>
+      <c r="K37" t="s">
+        <v>223</v>
+      </c>
+      <c r="L37" t="s">
+        <v>224</v>
+      </c>
+      <c r="M37" t="s">
+        <v>222</v>
+      </c>
+      <c r="N37" t="s">
+        <v>223</v>
+      </c>
+      <c r="O37" t="s">
+        <v>224</v>
+      </c>
+      <c r="P37" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>223</v>
+      </c>
+      <c r="R37" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" s="18">
+        <f>AVERAGE(S38:S39)</f>
+        <v>41.68</v>
+      </c>
+      <c r="C38" s="18">
+        <f>AVERAGE(T38:T39)</f>
+        <v>1840.7550000000001</v>
+      </c>
+      <c r="D38" s="18">
+        <v>213</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="F38" s="18">
+        <f>C38*$E$5/$E$6*2*PI()/60</f>
+        <v>229.48025337534443</v>
+      </c>
+      <c r="G38" s="18">
+        <f>C38*$E$10/$E$6</f>
+        <v>2279.0300000000002</v>
+      </c>
+      <c r="H38" s="18">
+        <f>E38*D38</f>
+        <v>80.94</v>
+      </c>
+      <c r="I38" s="18">
+        <f>150*E38</f>
+        <v>57</v>
+      </c>
+      <c r="J38">
+        <v>8</v>
+      </c>
+      <c r="K38">
+        <v>22</v>
+      </c>
+      <c r="L38">
+        <v>70</v>
+      </c>
+      <c r="M38">
+        <v>8</v>
+      </c>
+      <c r="N38">
+        <v>23</v>
+      </c>
+      <c r="O38">
+        <v>52</v>
+      </c>
+      <c r="P38">
+        <v>884</v>
+      </c>
+      <c r="Q38">
+        <v>1711</v>
+      </c>
+      <c r="R38">
+        <v>2009</v>
+      </c>
+      <c r="S38">
+        <f>SUMPRODUCT(J38:L38,M38:O38)/SUM(J38:L38)</f>
+        <v>42.1</v>
+      </c>
+      <c r="T38">
+        <f>SUMPRODUCT(P38:R38,J38:L38)/SUM(J38:L38)</f>
+        <v>1853.44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="3"/>
+      <c r="J39">
+        <v>8</v>
+      </c>
+      <c r="K39">
+        <v>21</v>
+      </c>
+      <c r="L39">
+        <v>71</v>
+      </c>
+      <c r="M39">
+        <v>9</v>
+      </c>
+      <c r="N39">
+        <v>24</v>
+      </c>
+      <c r="O39">
+        <v>50</v>
+      </c>
+      <c r="P39">
+        <v>955</v>
+      </c>
+      <c r="Q39">
+        <v>1718</v>
+      </c>
+      <c r="R39">
+        <v>1959</v>
+      </c>
+      <c r="S39">
+        <f t="shared" ref="S39:S45" si="0">SUMPRODUCT(J39:L39,M39:O39)/SUM(J39:L39)</f>
+        <v>41.26</v>
+      </c>
+      <c r="T39">
+        <f t="shared" ref="T39:T45" si="1">SUMPRODUCT(P39:R39,J39:L39)/SUM(J39:L39)</f>
+        <v>1828.07</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="18">
+        <f>AVERAGE(S40:S42)</f>
+        <v>55.79</v>
+      </c>
+      <c r="C40" s="18">
+        <f>AVERAGE(T40:T41)</f>
+        <v>1791.8899999999999</v>
+      </c>
+      <c r="D40" s="18">
+        <v>215</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="F40" s="18">
+        <f>C40*$E$5/$E$6*2*PI()/60</f>
+        <v>223.3884309540085</v>
+      </c>
+      <c r="G40" s="18">
+        <f>C40*$E$10/$E$6</f>
+        <v>2218.5304761904763</v>
+      </c>
+      <c r="H40" s="18">
+        <f>E40*D40</f>
+        <v>103.2</v>
+      </c>
+      <c r="I40" s="18">
+        <f>150*E40</f>
+        <v>72</v>
+      </c>
+      <c r="J40">
+        <v>4</v>
+      </c>
+      <c r="K40">
+        <v>25</v>
+      </c>
+      <c r="L40">
+        <v>71</v>
+      </c>
+      <c r="M40">
+        <v>13</v>
+      </c>
+      <c r="N40">
+        <v>33</v>
+      </c>
+      <c r="O40">
+        <v>66</v>
+      </c>
+      <c r="P40">
+        <v>1455</v>
+      </c>
+      <c r="Q40">
+        <v>1568</v>
+      </c>
+      <c r="R40">
+        <v>1767</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="0"/>
+        <v>55.63</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="1"/>
+        <v>1704.77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="3"/>
+      <c r="J41">
+        <v>3</v>
+      </c>
+      <c r="K41">
+        <v>27</v>
+      </c>
+      <c r="L41">
+        <v>70</v>
+      </c>
+      <c r="M41">
+        <v>13</v>
+      </c>
+      <c r="N41">
+        <v>35</v>
+      </c>
+      <c r="O41">
+        <v>68</v>
+      </c>
+      <c r="P41">
+        <v>1543</v>
+      </c>
+      <c r="Q41">
+        <v>1696</v>
+      </c>
+      <c r="R41">
+        <v>1964</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="0"/>
+        <v>57.44</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="1"/>
+        <v>1879.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="3"/>
+      <c r="J42">
+        <v>3</v>
+      </c>
+      <c r="K42">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>73</v>
+      </c>
+      <c r="M42">
+        <v>13</v>
+      </c>
+      <c r="N42">
+        <v>33</v>
+      </c>
+      <c r="O42">
+        <v>63</v>
+      </c>
+      <c r="P42">
+        <v>905</v>
+      </c>
+      <c r="Q42">
+        <v>1541</v>
+      </c>
+      <c r="R42">
+        <v>1827</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="0"/>
+        <v>54.3</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="1"/>
+        <v>1730.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" t="s">
+        <v>227</v>
+      </c>
+      <c r="B43" s="18">
+        <f>AVERAGE(S43:S45)</f>
+        <v>73.423333333333332</v>
+      </c>
+      <c r="C43" s="18">
+        <f>AVERAGE(T43:T44)</f>
+        <v>1395.97</v>
+      </c>
+      <c r="D43" s="18">
+        <v>220</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.59</v>
+      </c>
+      <c r="F43" s="18">
+        <f>C43*$E$5/$E$6*2*PI()/60</f>
+        <v>174.0305197076089</v>
+      </c>
+      <c r="G43" s="18">
+        <f>C43*$E$10/$E$6</f>
+        <v>1728.3438095238096</v>
+      </c>
+      <c r="H43" s="18">
+        <f>E43*D43</f>
+        <v>129.79999999999998</v>
+      </c>
+      <c r="I43" s="18">
+        <f>150*E43</f>
+        <v>88.5</v>
+      </c>
+      <c r="J43">
+        <v>41</v>
+      </c>
+      <c r="K43">
+        <v>59</v>
+      </c>
+      <c r="M43">
+        <v>37</v>
+      </c>
+      <c r="N43">
+        <v>76</v>
+      </c>
+      <c r="P43">
+        <v>904</v>
+      </c>
+      <c r="Q43">
+        <v>1514</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="0"/>
+        <v>60.01</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="1"/>
+        <v>1263.9000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="J44">
+        <v>4</v>
+      </c>
+      <c r="K44">
+        <v>96</v>
+      </c>
+      <c r="M44">
+        <v>36</v>
+      </c>
+      <c r="N44">
+        <v>81</v>
+      </c>
+      <c r="P44">
+        <v>1433</v>
+      </c>
+      <c r="Q44">
+        <v>1532</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="0"/>
+        <v>79.2</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="1"/>
+        <v>1528.04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>98</v>
+      </c>
+      <c r="M45">
+        <v>35</v>
+      </c>
+      <c r="N45">
+        <v>82</v>
+      </c>
+      <c r="P45">
+        <v>1492</v>
+      </c>
+      <c r="Q45">
+        <v>1545</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="0"/>
+        <v>81.06</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="1"/>
+        <v>1543.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50BA889-C2C3-44BD-B36B-00B461F7893B}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.34998626667073579"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="21.26953125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="44.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="49.26953125" customWidth="1"/>
+    <col min="5" max="5" width="58.453125" customWidth="1"/>
+    <col min="6" max="6" width="63.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="25">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="25">
+        <v>2014</v>
+      </c>
+      <c r="D2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="25">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="25">
+        <v>2016</v>
+      </c>
+      <c r="D3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="25">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="25">
+        <v>2020</v>
+      </c>
+      <c r="D4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="25">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="25">
+        <v>2022</v>
+      </c>
+      <c r="D5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="25">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="25">
+        <v>2021</v>
+      </c>
+      <c r="D6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="25">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="25">
+        <v>2018</v>
+      </c>
+      <c r="D7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="25">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="25">
+        <v>2015</v>
+      </c>
+      <c r="D8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="25">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="25">
+        <v>2025</v>
+      </c>
+      <c r="D9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{CEE54E0D-820C-4C83-AD48-EB04F0937B00}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{F414B4AA-25B5-4AAF-A8DC-E3CA7156B3A5}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{57E76D6B-8CB5-4A9D-AA0F-248DF88F03A6}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{75BD29B1-C55E-4763-AAF4-4EA108BAE6EE}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{97427FC5-9861-4614-A41D-5CD823AF48B2}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{18AE7998-2895-442D-9900-3B6CDA173B7F}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{EA573569-0785-48D8-84E2-1B88E9D408DF}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{5C852D94-5D32-4EE3-9361-ED2F31AA9B5F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E5BCB7-B0F6-4E3B-8F08-5A1471634CD0}">
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
@@ -1940,8 +3760,8 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I2" s="12">
-        <f>AVERAGE(B2:H2)</f>
-        <v>0.79286445440132458</v>
+        <f>AVERAGE(Other!C11:C13)*(1+Other!E23)^(2050-2021)</f>
+        <v>1.2256526492446329</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1977,8 +3797,8 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I3" s="12">
-        <f t="shared" ref="I3:I13" si="1">AVERAGE(B3:H3)</f>
-        <v>1.4748394199907213</v>
+        <f>AVERAGE(Other!C5:C6)*(1+Other!E21)^(2050-2021)</f>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2010,12 +3830,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H4" s="12">
-        <f t="shared" ref="H4:H13" si="2">H3</f>
+        <f t="shared" ref="H4:H13" si="1">H3</f>
         <v>1.4084507042253522</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.3584277010381676</v>
+        <f>$I$3</f>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2031,11 +3851,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D5" s="12">
-        <f t="shared" ref="D5:D13" si="3">D4</f>
+        <f t="shared" ref="D5:D13" si="2">D4</f>
         <v>2.1291509681941645</v>
       </c>
       <c r="E5" s="12">
-        <f t="shared" ref="E5:E10" si="4">$E$3</f>
+        <f t="shared" ref="E5:E10" si="3">$E$3</f>
         <v>1.8148820326678765</v>
       </c>
       <c r="F5" s="12">
@@ -2047,12 +3867,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" si="1"/>
-        <v>1.4748394199907213</v>
+        <f t="shared" ref="I5:I13" si="4">$I$3</f>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2068,11 +3888,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D6" s="12">
+        <f t="shared" si="2"/>
+        <v>2.1291509681941645</v>
+      </c>
+      <c r="E6" s="12">
         <f t="shared" si="3"/>
-        <v>2.1291509681941645</v>
-      </c>
-      <c r="E6" s="12">
-        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F6" s="12">
@@ -2084,12 +3904,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H6" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I6" s="12">
-        <f t="shared" si="1"/>
-        <v>1.4748394199907213</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2104,11 +3924,11 @@
         <v>1.05</v>
       </c>
       <c r="D7" s="12">
+        <f t="shared" si="2"/>
+        <v>2.1291509681941645</v>
+      </c>
+      <c r="E7" s="12">
         <f t="shared" si="3"/>
-        <v>2.1291509681941645</v>
-      </c>
-      <c r="E7" s="12">
-        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F7" s="12">
@@ -2120,12 +3940,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H7" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I7" s="12">
-        <f t="shared" si="1"/>
-        <v>1.4740875402914733</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2141,11 +3961,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D8" s="12">
+        <f t="shared" si="2"/>
+        <v>2.1291509681941645</v>
+      </c>
+      <c r="E8" s="12">
         <f t="shared" si="3"/>
-        <v>2.1291509681941645</v>
-      </c>
-      <c r="E8" s="12">
-        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F8" s="12">
@@ -2157,12 +3977,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H8" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I8" s="12">
-        <f t="shared" si="1"/>
-        <v>1.4748394199907213</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2178,11 +3998,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D9" s="12">
+        <f t="shared" si="2"/>
+        <v>2.1291509681941645</v>
+      </c>
+      <c r="E9" s="12">
         <f t="shared" si="3"/>
-        <v>2.1291509681941645</v>
-      </c>
-      <c r="E9" s="12">
-        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F9" s="12">
@@ -2194,12 +4014,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H9" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I9" s="12">
-        <f t="shared" si="1"/>
-        <v>1.4748394199907213</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2215,11 +4035,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D10" s="12">
+        <f t="shared" si="2"/>
+        <v>2.1291509681941645</v>
+      </c>
+      <c r="E10" s="12">
         <f t="shared" si="3"/>
-        <v>2.1291509681941645</v>
-      </c>
-      <c r="E10" s="12">
-        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F10" s="12">
@@ -2231,12 +4051,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="1"/>
-        <v>1.4748394199907213</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2252,7 +4072,7 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D11" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E11" s="12">
@@ -2268,12 +4088,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" si="1"/>
-        <v>1.3584277010381676</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2289,7 +4109,7 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E12" s="12">
@@ -2305,12 +4125,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="1"/>
-        <v>1.3584277010381676</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2326,7 +4146,7 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E13" s="12">
@@ -2342,12 +4162,12 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4084507042253522</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="1"/>
-        <v>1.3584277010381676</v>
+        <f t="shared" si="4"/>
+        <v>2.5249452352579165</v>
       </c>
     </row>
     <row r="14" spans="1:9">

--- a/InputData/indst/IEMUEF/Indst Eqpt Min Unit E Factor.xlsx
+++ b/InputData/indst/IEMUEF/Indst Eqpt Min Unit E Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IEMUEF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADEAAB6-28F7-40BD-9A4D-9855BE142785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7618BB77-715B-43BD-8831-66D9370D4AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="260" windowWidth="17790" windowHeight="9120" tabRatio="684" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="684" firstSheet="6" activeTab="12" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,19 +22,19 @@
     <sheet name="High Temp" sheetId="12" r:id="rId7"/>
     <sheet name="Cooling" sheetId="11" r:id="rId8"/>
     <sheet name="Electrochemical" sheetId="14" r:id="rId9"/>
-    <sheet name="Other" sheetId="15" r:id="rId10"/>
-    <sheet name="References" sheetId="16" r:id="rId11"/>
-    <sheet name="IEMUEF" sheetId="2" r:id="rId12"/>
+    <sheet name="Lighting" sheetId="18" r:id="rId10"/>
+    <sheet name="Other" sheetId="15" r:id="rId11"/>
+    <sheet name="References" sheetId="16" r:id="rId12"/>
+    <sheet name="IEMUEF" sheetId="2" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
   </externalReferences>
   <definedNames>
     <definedName name="base.year">#REF!</definedName>
-    <definedName name="CH4_to_CO2e">'[2]Cross-Page Data'!$C$12</definedName>
+    <definedName name="CH4_to_CO2e">'[1]Cross-Page Data'!$C$12</definedName>
     <definedName name="CH4GWP">#REF!</definedName>
     <definedName name="coal.past">#REF!</definedName>
     <definedName name="Constants.Density.Diesel">#REF!</definedName>
@@ -74,7 +74,7 @@
     <definedName name="EF.NaturalGas.CO2">#REF!</definedName>
     <definedName name="EF.NaturalGas.N2O">#REF!</definedName>
     <definedName name="GBP">#REF!</definedName>
-    <definedName name="gigwatts_to_megawatts">[3]About!$A$31</definedName>
+    <definedName name="gigwatts_to_megawatts">[2]About!$A$31</definedName>
     <definedName name="growth.scenario">#REF!</definedName>
     <definedName name="GWP.CH4">#REF!</definedName>
     <definedName name="GWP.N2O">#REF!</definedName>
@@ -105,7 +105,7 @@
     <definedName name="IX.a.scenario">#REF!</definedName>
     <definedName name="MGBP">#REF!</definedName>
     <definedName name="Minesize.xv.b">#REF!</definedName>
-    <definedName name="N2O_to_CO2e">'[2]Cross-Page Data'!$C$13</definedName>
+    <definedName name="N2O_to_CO2e">'[1]Cross-Page Data'!$C$13</definedName>
     <definedName name="N2OGWP">#REF!</definedName>
     <definedName name="nuclear.past">#REF!</definedName>
     <definedName name="plantsize.I.b">#REF!</definedName>
@@ -180,7 +180,7 @@
     <definedName name="Unit.TWh">#REF!</definedName>
     <definedName name="Unit.W">#REF!</definedName>
     <definedName name="Unit.year">#REF!</definedName>
-    <definedName name="unit_conv">[4]About!$A$123</definedName>
+    <definedName name="unit_conv">[3]About!$A$123</definedName>
     <definedName name="USD_Bn">#REF!</definedName>
     <definedName name="USD_mn">#REF!</definedName>
     <definedName name="USD2012_">#REF!</definedName>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="291">
   <si>
     <t>Source:</t>
   </si>
@@ -319,9 +319,6 @@
   </si>
   <si>
     <t>Machine Drive</t>
-  </si>
-  <si>
-    <t>Electrochem</t>
   </si>
   <si>
     <t>Other process</t>
@@ -1112,6 +1109,75 @@
   </si>
   <si>
     <t>Electric</t>
+  </si>
+  <si>
+    <t>https://www.mordorintelligence.com/industry-reports/industrial-lighting-market</t>
+  </si>
+  <si>
+    <t>Industrial lighting market</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>Fluorescent</t>
+  </si>
+  <si>
+    <t>HID fixtures</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>https://www.gelighting.com/inform/guide-energy-efficient-light-bulbs</t>
+  </si>
+  <si>
+    <t>Bulb efficiencies</t>
+  </si>
+  <si>
+    <t>Fluoresecent</t>
+  </si>
+  <si>
+    <t>Incandescent</t>
+  </si>
+  <si>
+    <t>HID</t>
+  </si>
+  <si>
+    <t>(assumption)</t>
+  </si>
+  <si>
+    <t>Max effic</t>
+  </si>
+  <si>
+    <t>Avg effic</t>
+  </si>
+  <si>
+    <t>assumption for LEDs</t>
+  </si>
+  <si>
+    <t>Facility HVAC</t>
+  </si>
+  <si>
+    <t>Facility lighting</t>
+  </si>
+  <si>
+    <t>Other nonprocess</t>
+  </si>
+  <si>
+    <t>Lighting is powered by electricity. To use other fuels one can use a generator</t>
+  </si>
+  <si>
+    <t>Avg efficiency</t>
+  </si>
+  <si>
+    <t>Avg intensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We assume a 35% generator efficiency to start. Assume a 5% improvement for best possible. </t>
+  </si>
+  <si>
+    <t>min intensity</t>
   </si>
 </sst>
 </file>
@@ -1917,42 +1983,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="About"/>
-      <sheetName val="EIA MECS Table 5.2"/>
-      <sheetName val="Med-High Temp Heat"/>
-      <sheetName val="Low Temp Heat"/>
-      <sheetName val="Cooling"/>
-      <sheetName val="Other"/>
-      <sheetName val="Efficiencies"/>
-      <sheetName val="Temperature Breakdown"/>
-      <sheetName val="References"/>
-      <sheetName val="Mapping"/>
-      <sheetName val="PIFURfE"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
       <sheetName val="Cross-Page Data"/>
@@ -2052,7 +2082,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2089,7 +2119,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2468,14 +2498,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E490AE5-9E06-4EDB-8D15-DE332404A026}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2483,12 +2513,12 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2498,27 +2528,27 @@
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2528,27 +2558,27 @@
     </row>
     <row r="13" spans="1:2">
       <c r="B13" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="2:2">
@@ -2558,27 +2588,27 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="2:2">
@@ -2588,92 +2618,92 @@
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2683,7 +2713,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2701,20 +2731,186 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B36B9AF-91BF-4AE1-AC7D-656F8CA0E617}">
+  <dimension ref="A2:C26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="C4" s="14"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="C5" s="14"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6">
+        <v>0.20050000000000001</v>
+      </c>
+      <c r="C6" s="14"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B13" s="11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B16" s="11">
+        <f>B11*B4+B12*B5+B6*B14+B11*B7</f>
+        <v>0.85307500000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19">
+        <f>1/B18</f>
+        <v>1.075268817204301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>287</v>
+      </c>
+      <c r="B25" s="11">
+        <f>B18*A23</f>
+        <v>0.37200000000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26">
+        <f>1/B25</f>
+        <v>2.6881720430107525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21FF5BE-8B42-4F7D-84E0-F7A55E52FE3E}">
   <dimension ref="A1:T45"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2734,12 +2930,12 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2749,30 +2945,30 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="C4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" t="s">
         <v>185</v>
       </c>
-      <c r="C4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>186</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>187</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>188</v>
-      </c>
-      <c r="H4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" s="27">
         <v>0.30299999999999999</v>
@@ -2791,12 +2987,12 @@
         <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6" s="27">
         <f>AVERAGE(0.35,0.305,0.266)</f>
@@ -2807,7 +3003,7 @@
         <v>3.2573289902280131</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E6">
         <v>2100</v>
@@ -2818,7 +3014,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
@@ -2828,18 +3024,18 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>185</v>
-      </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10">
         <f>AVERAGE(0.836,0.885,0.905)</f>
@@ -2850,7 +3046,7 @@
         <v>1.1424219345011424</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E10">
         <v>2600</v>
@@ -2861,7 +3057,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B11">
         <f>B10*(1-AVERAGE(0.1,0.15))</f>
@@ -2873,12 +3069,12 @@
       </c>
       <c r="D11" s="28"/>
       <c r="F11" s="28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B12">
         <f>1/C12</f>
@@ -2897,7 +3093,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13">
         <f>1/C13</f>
@@ -2914,7 +3110,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2924,7 +3120,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B16" s="14">
         <f>(AVERAGE(C5:C6)-AVERAGE(C11:C13))/AVERAGE(C5:C6)</f>
@@ -2937,13 +3133,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2953,27 +3149,27 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E20" t="s">
         <v>262</v>
       </c>
-      <c r="C20" t="s">
-        <v>260</v>
-      </c>
-      <c r="D20" t="s">
-        <v>261</v>
-      </c>
-      <c r="E20" t="s">
-        <v>263</v>
-      </c>
       <c r="H20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B21" s="32">
         <f>-0.041</f>
@@ -2991,12 +3187,12 @@
         <v>-8.968750000000001E-3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -3012,109 +3208,109 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
+        <v>203</v>
+      </c>
+      <c r="D35" t="s">
         <v>204</v>
-      </c>
-      <c r="D35" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s">
         <v>206</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D36" t="s">
         <v>207</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>208</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>209</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>210</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>211</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>212</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>213</v>
       </c>
-      <c r="J36" t="s">
+      <c r="M36" t="s">
         <v>214</v>
       </c>
-      <c r="M36" t="s">
+      <c r="P36" t="s">
         <v>215</v>
       </c>
-      <c r="P36" t="s">
+      <c r="S36" t="s">
         <v>216</v>
       </c>
-      <c r="S36" t="s">
+      <c r="T36" t="s">
         <v>217</v>
-      </c>
-      <c r="T36" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" t="s">
         <v>219</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>220</v>
       </c>
-      <c r="C37" t="s">
+      <c r="J37" t="s">
         <v>221</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>222</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>223</v>
       </c>
-      <c r="L37" t="s">
-        <v>224</v>
-      </c>
       <c r="M37" t="s">
+        <v>221</v>
+      </c>
+      <c r="N37" t="s">
         <v>222</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>223</v>
       </c>
-      <c r="O37" t="s">
-        <v>224</v>
-      </c>
       <c r="P37" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q37" t="s">
         <v>222</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>223</v>
-      </c>
-      <c r="R37" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B38" s="18">
         <f>AVERAGE(S38:S39)</f>
@@ -3225,7 +3421,7 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B40" s="18">
         <f>AVERAGE(S40:S42)</f>
@@ -3377,7 +3573,7 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B43" s="18">
         <f>AVERAGE(S43:S45)</f>
@@ -3498,40 +3694,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50BA889-C2C3-44BD-B36B-00B461F7893B}">
   <sheetPr>
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.26953125" style="25" customWidth="1"/>
-    <col min="2" max="2" width="44.54296875" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" style="25" customWidth="1"/>
-    <col min="4" max="4" width="49.26953125" customWidth="1"/>
-    <col min="5" max="5" width="58.453125" customWidth="1"/>
-    <col min="6" max="6" width="63.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="44.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="49.28515625" customWidth="1"/>
+    <col min="5" max="5" width="58.42578125" customWidth="1"/>
+    <col min="6" max="6" width="63.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3539,16 +3735,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C2" s="25">
         <v>2014</v>
       </c>
       <c r="D2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>236</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3556,16 +3752,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C3" s="25">
         <v>2016</v>
       </c>
       <c r="D3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>239</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3573,16 +3769,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C4" s="25">
         <v>2020</v>
       </c>
       <c r="D4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>242</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3590,16 +3786,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C5" s="25">
         <v>2022</v>
       </c>
       <c r="D5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3607,16 +3803,16 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C6" s="25">
         <v>2021</v>
       </c>
       <c r="D6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>248</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3624,16 +3820,16 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C7" s="25">
         <v>2018</v>
       </c>
       <c r="D7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>251</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3641,16 +3837,16 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C8" s="25">
         <v>2015</v>
       </c>
       <c r="D8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>253</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3658,16 +3854,16 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" s="25">
         <v>2025</v>
       </c>
       <c r="D9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>255</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3686,19 +3882,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E5BCB7-B0F6-4E3B-8F08-5A1471634CD0}">
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.81640625" customWidth="1"/>
+    <col min="2" max="11" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -3724,10 +3920,16 @@
         <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>283</v>
+      </c>
+      <c r="J1" t="s">
+        <v>284</v>
+      </c>
+      <c r="K1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -3760,11 +3962,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I2" s="12">
+        <f>B2</f>
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="12">
+        <f>Lighting!B19</f>
+        <v>1.075268817204301</v>
+      </c>
+      <c r="K2" s="12">
         <f>AVERAGE(Other!C11:C13)*(1+Other!E23)^(2050-2021)</f>
         <v>1.2256526492446329</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3797,11 +4007,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I3" s="12">
+        <f>B3</f>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J3" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K3" s="12">
         <f>AVERAGE(Other!C5:C6)*(1+Other!E21)^(2050-2021)</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3834,11 +4052,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I4" s="12">
-        <f>$I$3</f>
+        <f t="shared" ref="I4:I13" si="2">B4</f>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J4" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K4" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -3851,11 +4077,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D5" s="12">
-        <f t="shared" ref="D5:D13" si="2">D4</f>
+        <f t="shared" ref="D5:D13" si="3">D4</f>
         <v>2.1291509681941645</v>
       </c>
       <c r="E5" s="12">
-        <f t="shared" ref="E5:E10" si="3">$E$3</f>
+        <f t="shared" ref="E5:E10" si="4">$E$3</f>
         <v>1.8148820326678765</v>
       </c>
       <c r="F5" s="12">
@@ -3871,11 +4097,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" ref="I5:I13" si="4">$I$3</f>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J5" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K5" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3888,11 +4122,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D6" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E6" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F6" s="12">
@@ -3908,11 +4142,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I6" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J6" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K6" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3924,11 +4166,11 @@
         <v>1.05</v>
       </c>
       <c r="D7" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E7" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F7" s="12">
@@ -3944,11 +4186,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I7" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.05</v>
+      </c>
+      <c r="J7" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K7" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3961,11 +4211,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D8" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F8" s="12">
@@ -3981,11 +4231,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I8" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J8" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K8" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -3998,11 +4256,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D9" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E9" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F9" s="12">
@@ -4018,11 +4276,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I9" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J9" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K9" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -4035,11 +4301,11 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E10" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.8148820326678765</v>
       </c>
       <c r="F10" s="12">
@@ -4055,11 +4321,19 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J10" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K10" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -4072,7 +4346,7 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E11" s="12">
@@ -4092,13 +4366,21 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J11" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K11" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="12">
         <f t="shared" si="5"/>
@@ -4109,7 +4391,7 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E12" s="12">
@@ -4129,13 +4411,21 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J12" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K12" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="12">
         <f t="shared" si="5"/>
@@ -4146,7 +4436,7 @@
         <v>1.0526315789473684</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1291509681941645</v>
       </c>
       <c r="E13" s="12">
@@ -4166,19 +4456,17 @@
         <v>1.4084507042253522</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="J13" s="12">
+        <f>Lighting!$B$26</f>
+        <v>2.6881720430107525</v>
+      </c>
+      <c r="K13" s="12">
+        <f>$K$3</f>
         <v>2.5249452352579165</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4188,26 +4476,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208DE7CD-1195-47A7-9F7A-06312F92713C}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
         <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
       </c>
       <c r="F18">
         <v>2018</v>
@@ -4216,27 +4504,27 @@
         <v>2050</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>41</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>42</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>43</v>
       </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I19">
         <v>2021</v>
@@ -4245,18 +4533,18 @@
         <v>2050</v>
       </c>
       <c r="K19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" t="s">
         <v>45</v>
-      </c>
-      <c r="M19" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
         <v>47</v>
-      </c>
-      <c r="C20" t="s">
-        <v>48</v>
       </c>
       <c r="D20">
         <v>0.218</v>
@@ -4289,10 +4577,10 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>2.1999999999999999E-2</v>
@@ -4325,10 +4613,10 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>0.20399999999999999</v>
@@ -4361,10 +4649,10 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23">
         <v>3.9E-2</v>
@@ -4397,10 +4685,10 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24">
         <v>1.2999999999999999E-2</v>
@@ -4433,10 +4721,10 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>0.19900000000000001</v>
@@ -4469,10 +4757,10 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D26">
         <v>1E-3</v>
@@ -4505,10 +4793,10 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27">
         <v>1.0999999999999999E-2</v>
@@ -4541,10 +4829,10 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28">
         <v>7.0000000000000001E-3</v>
@@ -4584,52 +4872,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E6737B-14AA-41CE-9388-6419CF592696}">
   <dimension ref="H2:O36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.1796875" customWidth="1"/>
-    <col min="11" max="11" width="30.7265625" customWidth="1"/>
-    <col min="12" max="12" width="22.1796875" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" customWidth="1"/>
     <col min="13" max="13" width="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.1796875" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="8:15">
       <c r="H2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="8:15">
       <c r="H3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="8:15" s="9" customFormat="1" ht="45">
+      <c r="I4" s="9" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="8:15" s="9" customFormat="1" ht="43.5">
-      <c r="I4" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="J4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="L4" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="8:15">
       <c r="L5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="8:15">
       <c r="I6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>83</v>
@@ -4638,7 +4926,7 @@
         <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M6">
         <v>90.1</v>
@@ -4653,7 +4941,7 @@
     </row>
     <row r="7" spans="8:15">
       <c r="I7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -4662,7 +4950,7 @@
         <v>89</v>
       </c>
       <c r="L7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M7">
         <v>93.1</v>
@@ -4677,7 +4965,7 @@
     </row>
     <row r="8" spans="8:15">
       <c r="I8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8">
         <v>92</v>
@@ -4686,7 +4974,7 @@
         <v>91</v>
       </c>
       <c r="L8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M8">
         <v>94.7</v>
@@ -4701,7 +4989,7 @@
     </row>
     <row r="9" spans="8:15">
       <c r="I9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J9">
         <v>93</v>
@@ -4710,7 +4998,7 @@
         <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M9">
         <v>95.9</v>
@@ -4725,7 +5013,7 @@
     </row>
     <row r="10" spans="8:15">
       <c r="I10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J10">
         <v>93</v>
@@ -4734,7 +5022,7 @@
         <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M10">
         <v>96.2</v>
@@ -4749,7 +5037,7 @@
     </row>
     <row r="11" spans="8:15">
       <c r="I11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J11">
         <v>93</v>
@@ -4758,7 +5046,7 @@
         <v>94</v>
       </c>
       <c r="L11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M11">
         <v>96.2</v>
@@ -4773,7 +5061,7 @@
     </row>
     <row r="12" spans="8:15">
       <c r="I12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>93</v>
@@ -4792,7 +5080,7 @@
     </row>
     <row r="13" spans="8:15">
       <c r="I13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J13">
         <v>92</v>
@@ -4811,7 +5099,7 @@
     </row>
     <row r="14" spans="8:15">
       <c r="I14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14">
         <v>86</v>
@@ -4830,13 +5118,13 @@
     </row>
     <row r="15" spans="8:15">
       <c r="I15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J15">
         <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M15">
         <f>M14</f>
@@ -4849,23 +5137,23 @@
     </row>
     <row r="17" spans="9:12">
       <c r="J17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="9:12">
       <c r="I18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J18" s="18">
         <v>25.980397752045299</v>
       </c>
       <c r="L18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="9:12">
       <c r="I19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J19" s="18">
         <v>67.647063795395397</v>
@@ -4876,18 +5164,18 @@
     </row>
     <row r="20" spans="9:12">
       <c r="I20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J20" s="18">
         <v>86.928108261286297</v>
       </c>
       <c r="L20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="9:12">
       <c r="I21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J21" s="18">
         <v>71.895427750300499</v>
@@ -4895,7 +5183,7 @@
     </row>
     <row r="22" spans="9:12">
       <c r="I22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J22" s="18">
         <v>64.379085998847998</v>
@@ -4903,7 +5191,7 @@
     </row>
     <row r="23" spans="9:12">
       <c r="I23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J23" s="18">
         <v>94.281049327759803</v>
@@ -4911,7 +5199,7 @@
     </row>
     <row r="24" spans="9:12">
       <c r="I24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J24" s="18">
         <v>62.908497785553301</v>
@@ -4919,7 +5207,7 @@
     </row>
     <row r="25" spans="9:12">
       <c r="I25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J25" s="18">
         <v>34.803927031813501</v>
@@ -4927,7 +5215,7 @@
     </row>
     <row r="26" spans="9:12">
       <c r="I26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J26" s="18">
         <v>17.6470525756977</v>
@@ -4935,7 +5223,7 @@
     </row>
     <row r="27" spans="9:12">
       <c r="I27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J27" s="18">
         <v>17.156856504599499</v>
@@ -4943,10 +5231,10 @@
     </row>
     <row r="29" spans="9:12">
       <c r="J29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="30" spans="9:12">
@@ -4971,7 +5259,7 @@
     </row>
     <row r="34" spans="10:11">
       <c r="J34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="10:11">
@@ -4979,7 +5267,7 @@
         <v>0.4</v>
       </c>
       <c r="K35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="10:11">
@@ -4988,7 +5276,7 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="K36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5000,22 +5288,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6325B5-8F49-4EFF-9AFE-787745135977}">
   <dimension ref="B24:D27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="24" spans="2:4">
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:4">
       <c r="B25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <f>1/C24</f>
@@ -5024,7 +5312,7 @@
     </row>
     <row r="26" spans="2:4">
       <c r="B26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -5032,14 +5320,14 @@
     </row>
     <row r="27" spans="2:4">
       <c r="B27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C27">
         <f>1/C26</f>
         <v>0.2</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -5051,10 +5339,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A620FBB6-6DA6-4445-A3B7-9FDC2FA0643B}">
   <dimension ref="B2:D25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="64.6328125" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -5073,15 +5361,15 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
         <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>0.75</v>
@@ -5093,7 +5381,7 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18">
         <v>0.81</v>
@@ -5105,7 +5393,7 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19">
         <v>0.82</v>
@@ -5117,7 +5405,7 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20">
         <v>0.83</v>
@@ -5129,7 +5417,7 @@
     </row>
     <row r="21" spans="2:4">
       <c r="B21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21">
         <v>0.83</v>
@@ -5141,7 +5429,7 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22">
         <v>0.7</v>
@@ -5153,7 +5441,7 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23">
         <v>0.7</v>
@@ -5165,7 +5453,7 @@
     </row>
     <row r="25" spans="2:4">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25">
         <v>0.95</v>
@@ -5184,42 +5472,42 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1A33F7-3B58-415B-8180-0D752D7B0DBE}">
   <dimension ref="I3:P15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="9:16">
       <c r="I3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="9:16">
       <c r="I4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" t="s">
         <v>76</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>171</v>
+      </c>
+      <c r="O4" t="s">
         <v>77</v>
       </c>
-      <c r="L4" t="s">
-        <v>172</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>78</v>
-      </c>
-      <c r="P4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="5" spans="9:16">
       <c r="I5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J5" s="17">
         <v>0.27800000000000002</v>
@@ -5229,7 +5517,7 @@
         <v>0.5</v>
       </c>
       <c r="N5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O5" s="11">
         <f>SUMPRODUCT(J6:J7,L6:L7)/SUM(J6:J7)</f>
@@ -5242,7 +5530,7 @@
     </row>
     <row r="6" spans="9:16">
       <c r="I6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J6" s="14">
         <f>SUM(12.1%,31.8%)</f>
@@ -5256,7 +5544,7 @@
         <v>0.71</v>
       </c>
       <c r="N6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O6" s="11">
         <f>SUMPRODUCT(J13:J14,L13:L14)/SUM(J13:J14)</f>
@@ -5269,7 +5557,7 @@
     </row>
     <row r="7" spans="9:16">
       <c r="I7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J7" s="17">
         <v>4.7E-2</v>
@@ -5284,7 +5572,7 @@
     </row>
     <row r="8" spans="9:16">
       <c r="I8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J8" s="17">
         <v>3.9E-2</v>
@@ -5296,26 +5584,26 @@
     </row>
     <row r="10" spans="9:16">
       <c r="I10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="9:16">
       <c r="I11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
         <v>76</v>
       </c>
-      <c r="K11" t="s">
-        <v>77</v>
-      </c>
       <c r="L11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="9:16">
       <c r="I12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J12" s="17">
         <v>0.27800000000000002</v>
@@ -5327,7 +5615,7 @@
     </row>
     <row r="13" spans="9:16">
       <c r="I13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J13" s="14">
         <f>SUM(12.1%,31.8%)</f>
@@ -5343,7 +5631,7 @@
     </row>
     <row r="14" spans="9:16">
       <c r="I14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J14" s="17">
         <v>4.7E-2</v>
@@ -5358,7 +5646,7 @@
     </row>
     <row r="15" spans="9:16">
       <c r="I15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J15" s="17">
         <v>3.9E-2</v>
@@ -5377,11 +5665,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE2796E-BC60-4177-9FEB-8E9F5425DFFA}">
   <dimension ref="A2:I22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:9">
       <c r="A2" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -5394,24 +5682,24 @@
     </row>
     <row r="3" spans="1:9">
       <c r="B3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4">
         <v>425</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E4">
         <f>AVERAGE(B4:B6)</f>
@@ -5424,32 +5712,32 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5">
         <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6">
         <v>400</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7">
         <f>1/G4</f>
@@ -5458,13 +5746,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B8">
         <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8">
         <f>AVERAGE(B8:B10)</f>
@@ -5473,29 +5761,29 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B9">
         <v>350</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B10">
         <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -5508,23 +5796,23 @@
     </row>
     <row r="13" spans="1:9">
       <c r="B13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B14" s="23">
         <v>0.504</v>
       </c>
       <c r="G14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G15">
         <f>1/B16</f>
@@ -5533,7 +5821,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B16" s="23">
         <v>0.55100000000000005</v>
@@ -5541,7 +5829,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -5554,10 +5842,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -5565,7 +5853,7 @@
         <v>1100</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G20">
         <f>B22/B22</f>
@@ -5574,10 +5862,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -5585,7 +5873,7 @@
         <v>793</v>
       </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G22">
         <f>1/G20</f>
@@ -5600,22 +5888,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9BDABE4-2D06-45EB-ACBA-FE104E27935D}">
   <dimension ref="B2:N37"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="J3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="2:11">
@@ -5663,39 +5951,39 @@
     </row>
     <row r="18" spans="2:14">
       <c r="B18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="2:14">
       <c r="I21" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="J23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K23" t="s">
+        <v>134</v>
+      </c>
+      <c r="L23" t="s">
         <v>135</v>
       </c>
-      <c r="L23" t="s">
-        <v>136</v>
-      </c>
       <c r="M23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="J24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K24">
         <v>0.79</v>
@@ -5715,7 +6003,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="J25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K25">
         <v>0.79</v>
@@ -5727,7 +6015,7 @@
     </row>
     <row r="26" spans="2:14">
       <c r="J26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K26">
         <v>0.71699999999999997</v>
@@ -5739,7 +6027,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="J27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K27">
         <v>0.63900000000000001</v>
@@ -5751,12 +6039,12 @@
     </row>
     <row r="28" spans="2:14">
       <c r="J28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="J29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K29">
         <v>0.70299999999999996</v>
@@ -5768,7 +6056,7 @@
     </row>
     <row r="30" spans="2:14">
       <c r="J30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K30">
         <v>0.63400000000000001</v>
@@ -5780,7 +6068,7 @@
     </row>
     <row r="31" spans="2:14">
       <c r="J31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K31">
         <v>0.57599999999999996</v>
@@ -5792,7 +6080,7 @@
     </row>
     <row r="32" spans="2:14">
       <c r="J32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K32">
         <v>0.57599999999999996</v>
@@ -5804,17 +6092,17 @@
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="2:2">
@@ -5832,16 +6120,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BF9617-11C7-43F5-9981-C4D048784240}">
   <dimension ref="A2:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B3" s="11">
         <v>0.61</v>
@@ -5849,12 +6137,12 @@
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" s="11">
         <v>0.7</v>
@@ -5862,12 +6150,12 @@
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="11">
         <v>0.61</v>
@@ -5875,12 +6163,12 @@
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B10" s="11">
         <v>0.72</v>
@@ -5888,7 +6176,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B12" s="11">
         <f>AVERAGE(B10,B5)</f>
@@ -5897,7 +6185,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13">
         <f>1/B12</f>
